--- a/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_65049_completo.xlsx
+++ b/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_65049_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4f89d76c74834d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Refc22cab762c4334"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,516 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6181</x:v>
+        <x:v>      6.0887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6181</x:v>
+        <x:v>      6.0887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3312</x:v>
+        <x:v>      6.8078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3312</x:v>
+        <x:v>      6.8078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3312</x:v>
+        <x:v>      6.8078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3312</x:v>
+        <x:v>      6.8078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3312</x:v>
+        <x:v>      6.8078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5936</x:v>
+        <x:v>      7.0609</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8691</x:v>
+        <x:v>      7.3208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8691</x:v>
+        <x:v>      7.3208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8691</x:v>
+        <x:v>      7.3208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7801</x:v>
+        <x:v>      8.1430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7801</x:v>
+        <x:v>      8.1430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7801</x:v>
+        <x:v>      8.1430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +3789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +3804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +3819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +3834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +3849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +3864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +3909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +3924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +3954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +3969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +3999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +4014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +4029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +4044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +4059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3654,7 +4164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3669,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3684,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3699,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3714,7 +4224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3729,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3744,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3759,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3774,7 +4284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3789,7 +4299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3804,7 +4314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3819,7 +4329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3834,7 +4344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3849,7 +4359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3864,7 +4374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3879,7 +4389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3894,7 +4404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3909,7 +4419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3924,7 +4434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3939,7 +4449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3954,7 +4464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3969,7 +4479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3984,7 +4494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3999,7 +4509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4014,7 +4524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4029,7 +4539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4044,7 +4554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4059,7 +4569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4074,7 +4584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4089,7 +4599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4104,7 +4614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4119,7 +4629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4134,7 +4644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4149,7 +4659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4164,7 +4674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4179,7 +4689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4194,7 +4704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4209,7 +4719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4224,7 +4734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4239,7 +4749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4254,7 +4764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4269,7 +4779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4284,7 +4794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9326</x:v>
+        <x:v>     10.6684</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4299,7 +4809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4314,7 +4824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4329,7 +4839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4344,7 +4854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4359,7 +4869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4374,7 +4884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4389,7 +4899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4404,7 +4914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4419,7 +4929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4434,7 +4944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4449,7 +4959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4464,7 +4974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4479,7 +4989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4494,7 +5004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4509,7 +5019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4524,7 +5034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4539,7 +5049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4554,7 +5064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4569,7 +5079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4584,7 +5094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4599,7 +5109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4614,7 +5124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4629,7 +5139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4644,7 +5154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4659,7 +5169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4674,7 +5184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4689,7 +5199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4704,7 +5214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4719,7 +5229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.4364</x:v>
+        <x:v>     11.7499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4734,7 +5244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.4364</x:v>
+        <x:v>     11.7499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4749,7 +5259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.4364</x:v>
+        <x:v>     11.7499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4764,7 +5274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.4364</x:v>
+        <x:v>     11.7499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4779,7 +5289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9825</x:v>
+        <x:v>     12.1278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4794,7 +5304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9825</x:v>
+        <x:v>     12.1278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4809,7 +5319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9825</x:v>
+        <x:v>     12.1278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4824,7 +5334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4839,7 +5349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4854,7 +5364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4869,7 +5379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4884,7 +5394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4899,7 +5409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4914,7 +5424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4929,7 +5439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4944,7 +5454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4959,7 +5469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4124</x:v>
+        <x:v>     13.7294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4974,7 +5484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4124</x:v>
+        <x:v>     13.7294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4989,7 +5499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4124</x:v>
+        <x:v>     13.7294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5004,7 +5514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5019,7 +5529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5034,7 +5544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5049,7 +5559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5064,7 +5574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5079,7 +5589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.2771</x:v>
+        <x:v>     15.4819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5094,7 +5604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.0682</x:v>
+        <x:v>     15.9446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5109,7 +5619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.0682</x:v>
+        <x:v>     15.9446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5124,7 +5634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5139,7 +5649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5154,7 +5664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4124</x:v>
+        <x:v>     13.7294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5169,7 +5679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5184,7 +5694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5199,7 +5709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5214,7 +5724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5229,7 +5739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5244,7 +5754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5259,7 +5769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5274,7 +5784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5289,7 +5799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5304,7 +5814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5319,7 +5829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5334,7 +5844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5349,7 +5859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5364,7 +5874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5379,7 +5889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5394,7 +5904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5409,7 +5919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5424,7 +5934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0061</x:v>
+        <x:v>      5.4273</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5439,7 +5949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0061</x:v>
+        <x:v>      5.4273</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5454,7 +5964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5469,7 +5979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5484,7 +5994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5499,7 +6009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5514,7 +6024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5529,7 +6039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5544,7 +6054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5559,7 +6069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5574,7 +6084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9326</x:v>
+        <x:v>     10.6684</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5589,7 +6099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9326</x:v>
+        <x:v>     10.6684</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5604,7 +6114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9326</x:v>
+        <x:v>     10.6684</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5619,7 +6129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5634,7 +6144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5649,7 +6159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5664,7 +6174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5679,7 +6189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5694,7 +6204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5709,7 +6219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5724,7 +6234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5739,7 +6249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5754,7 +6264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5769,7 +6279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5784,7 +6294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5799,7 +6309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.4364</x:v>
+        <x:v>     11.7499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5814,7 +6324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5829,7 +6339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5844,7 +6354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5859,7 +6369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5874,7 +6384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5889,7 +6399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5904,7 +6414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5919,7 +6429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5934,7 +6444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5949,7 +6459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5964,7 +6474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5979,7 +6489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5994,7 +6504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6009,7 +6519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6024,7 +6534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6039,7 +6549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6054,7 +6564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6069,7 +6579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.2771</x:v>
+        <x:v>     15.4819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6084,7 +6594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.2771</x:v>
+        <x:v>     15.4819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6099,7 +6609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6114,7 +6624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6129,7 +6639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     19.6373</x:v>
+        <x:v>     17.3942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6144,7 +6654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6159,7 +6669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6174,7 +6684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6189,7 +6699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6204,7 +6714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6219,7 +6729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6234,7 +6744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6249,7 +6759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6264,7 +6774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6279,7 +6789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6294,7 +6804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6309,7 +6819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6324,7 +6834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6339,7 +6849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6354,7 +6864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.9856</x:v>
+        <x:v>     23.5518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6369,7 +6879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.9856</x:v>
+        <x:v>     23.5518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6384,7 +6894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6399,7 +6909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6414,7 +6924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6429,7 +6939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6444,7 +6954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6459,7 +6969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6474,7 +6984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6489,7 +6999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6504,7 +7014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6519,7 +7029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6534,7 +7044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6549,7 +7059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.7390</x:v>
+        <x:v>     25.4787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6564,7 +7074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.7390</x:v>
+        <x:v>     25.4787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6579,7 +7089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6594,7 +7104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6609,7 +7119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6624,7 +7134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6639,7 +7149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6654,7 +7164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6669,7 +7179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6684,7 +7194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.1906</x:v>
+        <x:v>     28.2258</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6699,7 +7209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6714,7 +7224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6729,7 +7239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6744,7 +7254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4835</x:v>
+        <x:v>     35.3030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6759,7 +7269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4835</x:v>
+        <x:v>     35.3030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6774,7 +7284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6789,7 +7299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6804,7 +7314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6819,7 +7329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6834,7 +7344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6849,7 +7359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6864,7 +7374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6879,7 +7389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6894,7 +7404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6909,7 +7419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.0556</x:v>
+        <x:v>     40.0558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6924,7 +7434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.5412</x:v>
+        <x:v>     41.9877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6939,7 +7449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.2962</x:v>
+        <x:v>     42.9602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6954,7 +7464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6969,7 +7479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6288</x:v>
+        <x:v>     50.8984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6984,7 +7494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6999,7 +7509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7014,7 +7524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1931</x:v>
+        <x:v>     47.8886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7029,7 +7539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1931</x:v>
+        <x:v>     47.8886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7044,7 +7554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1931</x:v>
+        <x:v>     47.8886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7059,7 +7569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7074,7 +7584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7089,7 +7599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.8880</x:v>
+        <x:v>     37.1910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7104,7 +7614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.8880</x:v>
+        <x:v>     37.1910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7119,7 +7629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7134,7 +7644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7149,7 +7659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.6024</x:v>
+        <x:v>     38.1415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7164,7 +7674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7179,7 +7689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7194,7 +7704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7209,7 +7719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7224,7 +7734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7239,7 +7749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7254,7 +7764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7269,7 +7779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7284,7 +7794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7299,7 +7809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7314,7 +7824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7329,7 +7839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.8880</x:v>
+        <x:v>     37.1910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7344,7 +7854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.0556</x:v>
+        <x:v>     40.0558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7359,7 +7869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.5412</x:v>
+        <x:v>     41.9877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7374,7 +7884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7389,7 +7899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7404,7 +7914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7419,7 +7929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7434,7 +7944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7449,7 +7959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7464,7 +7974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7479,7 +7989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6288</x:v>
+        <x:v>     50.8984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7494,7 +8004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.8505</x:v>
+        <x:v>     56.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7509,7 +8019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.8505</x:v>
+        <x:v>     56.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7524,7 +8034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.9899</x:v>
+        <x:v>     54.9728</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7539,7 +8049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7554,7 +8064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.1021</x:v>
+        <x:v>     63.3324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7569,7 +8079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0277</x:v>
+        <x:v>     64.3971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7584,7 +8094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     60.8531</x:v>
+        <x:v>     67.6176</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7599,7 +8109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7614,7 +8124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7629,7 +8139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7644,7 +8154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.1021</x:v>
+        <x:v>     63.3324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7659,7 +8169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0277</x:v>
+        <x:v>     64.3971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7674,7 +8184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7773</x:v>
+        <x:v>     69.7865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7689,7 +8199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7704,7 +8214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7773</x:v>
+        <x:v>     69.7865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7719,7 +8229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.8112</x:v>
+        <x:v>     68.6998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7734,7 +8244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.7301</x:v>
+        <x:v>     75.2856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7749,7 +8259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7764,7 +8274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.7233</x:v>
+        <x:v>     74.1770</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7779,7 +8289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.4021</x:v>
+        <x:v>     97.1832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7794,7 +8304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.5713</x:v>
+        <x:v>     98.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7809,7 +8319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.0050</x:v>
+        <x:v>     83.1688</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7824,7 +8334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7839,7 +8349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7854,7 +8364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3407</x:v>
+        <x:v>     87.7700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7869,7 +8379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     78.2446</x:v>
+        <x:v>     86.6131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7884,7 +8394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7899,7 +8409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7914,7 +8424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7929,7 +8439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7944,7 +8454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.1566</x:v>
+        <x:v>     85.4606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7959,7 +8469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.1566</x:v>
+        <x:v>     85.4606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7974,7 +8484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.1566</x:v>
+        <x:v>     85.4606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7989,7 +8499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.4021</x:v>
+        <x:v>     97.1832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8004,7 +8514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8019,7 +8529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.3294</x:v>
+        <x:v>    103.2091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8034,7 +8544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.5713</x:v>
+        <x:v>     98.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8049,7 +8559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.8384</x:v>
+        <x:v>     79.7639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8064,7 +8574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     76.0767</x:v>
+        <x:v>     84.3125</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8079,7 +8589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     77.1566</x:v>
+        <x:v>     85.4606</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8094,7 +8604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8109,7 +8619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8124,7 +8634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.5713</x:v>
+        <x:v>     98.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8139,7 +8649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.7487</x:v>
+        <x:v>     99.5804</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8154,7 +8664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8169,7 +8679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8184,7 +8694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.0842</x:v>
+        <x:v>    116.8525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8199,7 +8709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.0842</x:v>
+        <x:v>    116.8525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8214,7 +8724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    114.6612</x:v>
+        <x:v>    123.2296</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8229,7 +8739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    124.2102</x:v>
+        <x:v>    132.3420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8244,7 +8754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    152.1348</x:v>
+        <x:v>    158.1598</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8259,7 +8769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    155.2448</x:v>
+        <x:v>    160.9697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8274,7 +8784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    147.5307</x:v>
+        <x:v>    153.9780</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8289,7 +8799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.8217</x:v>
+        <x:v>    131.0270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8304,7 +8814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8319,7 +8829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8334,7 +8844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.2745</x:v>
+        <x:v>    138.9825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8349,7 +8859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.0722</x:v>
+        <x:v>    144.3739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8364,7 +8874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    171.2820</x:v>
+        <x:v>    175.2824</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8379,7 +8889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    164.7697</x:v>
+        <x:v>    169.5046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8394,7 +8904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    135.6106</x:v>
+        <x:v>    143.0195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8409,7 +8919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.2745</x:v>
+        <x:v>    138.9825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8424,7 +8934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    138.5419</x:v>
+        <x:v>    145.7328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8439,7 +8949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    141.5057</x:v>
+        <x:v>    148.4636</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8454,7 +8964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    146.0123</x:v>
+        <x:v>    152.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8469,7 +8979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    161.5622</x:v>
+        <x:v>    166.6421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8484,7 +8994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8499,7 +9009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    164.7697</x:v>
+        <x:v>    169.5046</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8514,7 +9024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    144.5020</x:v>
+        <x:v>    151.2120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8529,7 +9039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    158.3873</x:v>
+        <x:v>    163.7971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8544,7 +9054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8559,7 +9069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    168.0096</x:v>
+        <x:v>    172.3847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8574,7 +9084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    155.2448</x:v>
+        <x:v>    160.9697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8589,7 +9099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    134.1571</x:v>
+        <x:v>    141.6694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8604,7 +9114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    132.7117</x:v>
+        <x:v>    140.3238</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8619,7 +9129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    134.1571</x:v>
+        <x:v>    141.6694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8634,7 +9144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.7487</x:v>
+        <x:v>     99.5804</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8649,7 +9159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     82.6778</x:v>
+        <x:v>     91.2670</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8664,7 +9174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    105.5102</x:v>
+        <x:v>    114.3324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8679,7 +9189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.7931</x:v>
+        <x:v>    115.5902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8694,7 +9204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.7487</x:v>
+        <x:v>     99.5804</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8709,7 +9219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8724,7 +9234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.7049</x:v>
+        <x:v>    127.1086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8739,7 +9249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.7049</x:v>
+        <x:v>    127.1086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8754,7 +9264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8769,7 +9279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8784,7 +9294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.0842</x:v>
+        <x:v>    116.8525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8799,7 +9309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8814,7 +9324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.3294</x:v>
+        <x:v>    103.2091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8829,7 +9339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.8384</x:v>
+        <x:v>     79.7639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8844,7 +9354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3407</x:v>
+        <x:v>     87.7700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8859,7 +9369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.8384</x:v>
+        <x:v>     79.7639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8874,7 +9384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8889,7 +9399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8904,7 +9414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8919,7 +9429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8934,7 +9444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8949,7 +9459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8964,7 +9474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.8505</x:v>
+        <x:v>     56.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8979,7 +9489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.8505</x:v>
+        <x:v>     56.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8994,7 +9504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.1374</x:v>
+        <x:v>     53.9476</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9009,7 +9519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9024,7 +9534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.3741</x:v>
+        <x:v>     60.1646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9039,7 +9549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.3741</x:v>
+        <x:v>     60.1646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9054,7 +9564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9069,7 +9579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9084,7 +9594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.5961</x:v>
+        <x:v>     58.0747</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9099,7 +9609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.5961</x:v>
+        <x:v>     58.0747</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9114,7 +9624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.5961</x:v>
+        <x:v>     58.0747</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9129,7 +9639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.4810</x:v>
+        <x:v>     59.1175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9144,7 +9654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.9614</x:v>
+        <x:v>     65.4662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9159,7 +9669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.9032</x:v>
+        <x:v>     66.5397</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9174,7 +9684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     61.8112</x:v>
+        <x:v>     68.6998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9189,7 +9699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9204,7 +9714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.0050</x:v>
+        <x:v>     83.1688</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9219,7 +9729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.9413</x:v>
+        <x:v>     82.0294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9234,7 +9744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9249,7 +9759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     86.0880</x:v>
+        <x:v>     94.8036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9264,7 +9774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     87.2410</x:v>
+        <x:v>     95.9912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9279,7 +9789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.5713</x:v>
+        <x:v>     98.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9294,7 +9804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9309,7 +9819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.2354</x:v>
+        <x:v>    113.0789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9324,7 +9834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.7931</x:v>
+        <x:v>    115.5902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9339,7 +9849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.7931</x:v>
+        <x:v>    115.5902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9354,7 +9864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.3833</x:v>
+        <x:v>    118.1191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9369,7 +9879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    150.5920</x:v>
+        <x:v>    156.7615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9384,7 +9894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    158.3873</x:v>
+        <x:v>    163.7971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9399,7 +9909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.0722</x:v>
+        <x:v>    144.3739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9414,7 +9924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    114.6612</x:v>
+        <x:v>    123.2296</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9429,7 +9939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    142.9998</x:v>
+        <x:v>    149.8356</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9444,7 +9954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    156.8120</x:v>
+        <x:v>    162.3812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9459,7 +9969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    152.1348</x:v>
+        <x:v>    158.1598</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9474,7 +9984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.3833</x:v>
+        <x:v>    118.1191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9489,7 +9999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9504,7 +10014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.0115</x:v>
+        <x:v>    134.9850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9519,7 +10029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.9687</x:v>
+        <x:v>    111.8298</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9534,7 +10044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.3294</x:v>
+        <x:v>    103.2091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9549,7 +10059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.8064</x:v>
+        <x:v>     92.4415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9564,7 +10074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.7301</x:v>
+        <x:v>     75.2856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9579,7 +10089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6288</x:v>
+        <x:v>     50.8984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9594,7 +10104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.0556</x:v>
+        <x:v>     40.0558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9609,7 +10119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.3975</x:v>
+        <x:v>     46.8942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9624,7 +10134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.2962</x:v>
+        <x:v>     42.9602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9639,7 +10149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9654,7 +10164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9669,7 +10179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9684,7 +10194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9699,7 +10209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4835</x:v>
+        <x:v>     35.3030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9714,7 +10224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9729,7 +10239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9744,7 +10254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.7943</x:v>
+        <x:v>     41.0196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9759,7 +10269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9774,7 +10284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9789,7 +10299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.6366</x:v>
+        <x:v>     20.0231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9804,7 +10314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.6366</x:v>
+        <x:v>     20.0231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9819,7 +10329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.5238</x:v>
+        <x:v>     18.4131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9834,7 +10344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.0682</x:v>
+        <x:v>     15.9446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9849,7 +10359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9864,7 +10374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     19.6373</x:v>
+        <x:v>     17.3942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9879,7 +10389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9894,7 +10404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9909,7 +10419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9924,7 +10434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9939,7 +10449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.5225</x:v>
+        <x:v>     18.9387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9954,7 +10464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     24.6366</x:v>
+        <x:v>     20.0231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9969,7 +10479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9984,7 +10494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9999,7 +10509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.1178</x:v>
+        <x:v>     21.7346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10014,7 +10524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.4651</x:v>
+        <x:v>     29.7445</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10029,7 +10539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10044,7 +10554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10059,7 +10569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10074,7 +10584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10089,7 +10599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10104,7 +10614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10119,7 +10629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.7390</x:v>
+        <x:v>     25.4787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10134,7 +10644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10149,7 +10659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10164,7 +10674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10179,7 +10689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10194,7 +10704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10209,7 +10719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10224,7 +10734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10239,7 +10749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7721</x:v>
+        <x:v>     31.5798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10254,7 +10764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7721</x:v>
+        <x:v>     31.5798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10269,7 +10779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.4377</x:v>
+        <x:v>     32.5040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10284,7 +10794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.4377</x:v>
+        <x:v>     32.5040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10299,7 +10809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.6024</x:v>
+        <x:v>     38.1415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10314,7 +10824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.6024</x:v>
+        <x:v>     38.1415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10329,7 +10839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.6024</x:v>
+        <x:v>     38.1415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10344,7 +10854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.8880</x:v>
+        <x:v>     37.1910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10359,7 +10869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.2962</x:v>
+        <x:v>     42.9602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10374,7 +10884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.2962</x:v>
+        <x:v>     42.9602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10389,7 +10899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     40.2962</x:v>
+        <x:v>     42.9602</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10404,7 +10914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10419,7 +10929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10434,7 +10944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10449,7 +10959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10464,7 +10974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.9969</x:v>
+        <x:v>     48.8875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10479,7 +10989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.4810</x:v>
+        <x:v>     59.1175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10494,7 +11004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10509,7 +11019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.0556</x:v>
+        <x:v>     40.0558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10524,7 +11034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.0556</x:v>
+        <x:v>     40.0558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10539,7 +11049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.7943</x:v>
+        <x:v>     41.0196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10554,7 +11064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.7943</x:v>
+        <x:v>     41.0196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10569,7 +11079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10584,7 +11094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10599,7 +11109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10614,7 +11124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10629,7 +11139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10644,7 +11154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.3975</x:v>
+        <x:v>     46.8942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10659,7 +11169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.9969</x:v>
+        <x:v>     48.8875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10674,7 +11184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10689,7 +11199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10704,7 +11214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.9969</x:v>
+        <x:v>     48.8875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10719,7 +11229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.2753</x:v>
+        <x:v>     61.2162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10734,7 +11244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.2753</x:v>
+        <x:v>     61.2162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10749,7 +11259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     56.1847</x:v>
+        <x:v>     62.2721</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10764,7 +11274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0277</x:v>
+        <x:v>     64.3971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10779,7 +11289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7773</x:v>
+        <x:v>     69.7865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10794,7 +11304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10809,7 +11319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.7233</x:v>
+        <x:v>     74.1770</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10824,7 +11334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.8858</x:v>
+        <x:v>     80.8945</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10839,7 +11349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     86.0880</x:v>
+        <x:v>     94.8036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10854,7 +11364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.4021</x:v>
+        <x:v>     97.1832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10869,7 +11379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     90.7487</x:v>
+        <x:v>     99.5804</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10884,7 +11394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10899,7 +11409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    110.6906</x:v>
+        <x:v>    119.3902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10914,7 +11424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.4598</x:v>
+        <x:v>    109.3448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10929,7 +11439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.9032</x:v>
+        <x:v>     66.5397</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10944,7 +11454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.1021</x:v>
+        <x:v>     63.3324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10959,7 +11469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.1374</x:v>
+        <x:v>     53.9476</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10974,7 +11484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -10989,7 +11499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11004,7 +11514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11019,7 +11529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11034,7 +11544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11049,7 +11559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11064,7 +11574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11079,7 +11589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11094,7 +11604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11109,7 +11619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6288</x:v>
+        <x:v>     50.8984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11124,7 +11634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     45.8088</x:v>
+        <x:v>     49.8907</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11139,7 +11649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7192</x:v>
+        <x:v>     57.0364</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11154,7 +11664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     51.7192</x:v>
+        <x:v>     57.0364</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11169,7 +11679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.4810</x:v>
+        <x:v>     59.1175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11184,7 +11694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.2753</x:v>
+        <x:v>     61.2162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11199,7 +11709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.1021</x:v>
+        <x:v>     63.3324</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11214,7 +11724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     59.9032</x:v>
+        <x:v>     66.5397</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11229,7 +11739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7773</x:v>
+        <x:v>     69.7865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11244,7 +11754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.7301</x:v>
+        <x:v>     75.2856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11259,7 +11769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7773</x:v>
+        <x:v>     69.7865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11274,7 +11784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     62.7773</x:v>
+        <x:v>     69.7865</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11289,7 +11799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.7233</x:v>
+        <x:v>     74.1770</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11304,7 +11814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11319,7 +11829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11334,7 +11844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11349,7 +11859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     86.0880</x:v>
+        <x:v>     94.8036</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11364,7 +11874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     96.7572</x:v>
+        <x:v>    105.6502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11379,7 +11889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.7931</x:v>
+        <x:v>    115.5902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11394,7 +11904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    108.0842</x:v>
+        <x:v>    116.8525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11409,7 +11919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11424,7 +11934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.0115</x:v>
+        <x:v>    134.9850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11439,7 +11949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.5392</x:v>
+        <x:v>    104.4275</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11454,7 +11964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     95.5392</x:v>
+        <x:v>    104.4275</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11469,7 +11979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     93.1277</x:v>
+        <x:v>    101.9952</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11484,7 +11994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.2174</x:v>
+        <x:v>    108.1089</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11499,7 +12009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    113.3296</x:v>
+        <x:v>    121.9454</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11514,7 +12024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.0690</x:v>
+        <x:v>    128.4103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11529,7 +12039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    124.2102</x:v>
+        <x:v>    132.3420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11544,7 +12054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11559,7 +12069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    142.9998</x:v>
+        <x:v>    149.8356</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11574,7 +12084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    155.2448</x:v>
+        <x:v>    160.9697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11589,7 +12099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    159.9707</x:v>
+        <x:v>    165.2174</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11604,7 +12114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.0690</x:v>
+        <x:v>    128.4103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11619,7 +12129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4413</x:v>
+        <x:v>    129.7165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11634,7 +12144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.0115</x:v>
+        <x:v>    134.9850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11649,7 +12159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.2745</x:v>
+        <x:v>    138.9825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11664,7 +12174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.8217</x:v>
+        <x:v>    131.0270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11679,7 +12189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    168.0096</x:v>
+        <x:v>    172.3847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11694,7 +12204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    169.6418</x:v>
+        <x:v>    173.8314</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11709,7 +12219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    179.6052</x:v>
+        <x:v>    182.6034</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11724,7 +12234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    168.0096</x:v>
+        <x:v>    172.3847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11739,7 +12249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    174.5869</x:v>
+        <x:v>    178.1976</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11754,7 +12264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11769,7 +12279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    207.6038</x:v>
+        <x:v>    206.7680</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11784,7 +12294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    209.4227</x:v>
+        <x:v>    208.3156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11799,7 +12309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    211.2498</x:v>
+        <x:v>    209.8676</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11814,7 +12324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    239.6304</x:v>
+        <x:v>    233.6743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11829,7 +12339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    237.6815</x:v>
+        <x:v>    232.0565</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11844,7 +12354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11859,7 +12369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    134.1571</x:v>
+        <x:v>    141.6694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11874,7 +12384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.8217</x:v>
+        <x:v>    131.0270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11889,7 +12399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11904,7 +12414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    124.2102</x:v>
+        <x:v>    132.3420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11919,7 +12429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    152.1348</x:v>
+        <x:v>    158.1598</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11934,7 +12444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    186.4099</x:v>
+        <x:v>    188.5392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11949,7 +12459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    195.0986</x:v>
+        <x:v>    196.0577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11964,7 +12474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    168.0096</x:v>
+        <x:v>    172.3847</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11979,7 +12489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.8217</x:v>
+        <x:v>    131.0270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -11994,7 +12504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4413</x:v>
+        <x:v>    129.7165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12009,7 +12519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4413</x:v>
+        <x:v>    129.7165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12024,7 +12534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    117.3489</x:v>
+        <x:v>    125.8112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12039,7 +12549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12054,7 +12564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12069,7 +12579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12084,7 +12594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.8217</x:v>
+        <x:v>    131.0270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12099,7 +12609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.2745</x:v>
+        <x:v>    138.9825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12114,7 +12624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.0722</x:v>
+        <x:v>    144.3739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12129,7 +12639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.0690</x:v>
+        <x:v>    128.4103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12144,7 +12654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12159,7 +12669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.0722</x:v>
+        <x:v>    144.3739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12174,7 +12684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    149.0573</x:v>
+        <x:v>    155.3675</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12189,7 +12699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    156.8120</x:v>
+        <x:v>    162.3812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12204,7 +12714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    152.1348</x:v>
+        <x:v>    158.1598</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12219,7 +12729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    172.9304</x:v>
+        <x:v>    176.7378</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12234,7 +12744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    182.9913</x:v>
+        <x:v>    185.5625</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12249,7 +12759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    207.6038</x:v>
+        <x:v>    206.7680</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12264,7 +12774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    209.4227</x:v>
+        <x:v>    208.3156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12279,7 +12789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    146.0123</x:v>
+        <x:v>    152.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12294,7 +12804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12309,7 +12819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12324,7 +12834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12339,7 +12849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    104.2354</x:v>
+        <x:v>    113.0789</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12354,7 +12864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12369,7 +12879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    117.3489</x:v>
+        <x:v>    125.8112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12384,7 +12894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    117.3489</x:v>
+        <x:v>    125.8112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12399,7 +12909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    174.5869</x:v>
+        <x:v>    178.1976</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12414,7 +12924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    186.4099</x:v>
+        <x:v>    188.5392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12429,7 +12939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    195.0986</x:v>
+        <x:v>    196.0577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12444,7 +12954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    195.0986</x:v>
+        <x:v>    196.0577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12459,7 +12969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    195.0986</x:v>
+        <x:v>    196.0577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12474,7 +12984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    211.2498</x:v>
+        <x:v>    209.8676</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12489,7 +12999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12504,7 +13014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.2745</x:v>
+        <x:v>    138.9825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12519,7 +13029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12534,7 +13044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12549,7 +13059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    101.7102</x:v>
+        <x:v>    110.5851</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12564,7 +13074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.3294</x:v>
+        <x:v>    103.2091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12579,7 +13089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4413</x:v>
+        <x:v>    129.7165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12594,7 +13104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4413</x:v>
+        <x:v>    129.7165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12609,7 +13119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    120.0690</x:v>
+        <x:v>    128.4103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12624,7 +13134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    117.3489</x:v>
+        <x:v>    125.8112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12639,7 +13149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12654,7 +13164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12669,7 +13179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    128.4244</x:v>
+        <x:v>    136.3131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12684,7 +13194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    117.3489</x:v>
+        <x:v>    125.8112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12699,7 +13209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12714,7 +13224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12729,7 +13239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     65.7246</x:v>
+        <x:v>     73.0728</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12744,7 +13254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.7233</x:v>
+        <x:v>     74.1770</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12759,7 +13269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.9413</x:v>
+        <x:v>     82.0294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12774,7 +13284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     70.7992</x:v>
+        <x:v>     78.6378</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12789,7 +13299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12804,7 +13314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12819,7 +13329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12834,7 +13344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12849,7 +13359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     38.7943</x:v>
+        <x:v>     41.0196</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12864,7 +13374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12879,7 +13389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12894,7 +13404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12909,7 +13419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12924,7 +13434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.5225</x:v>
+        <x:v>     18.9387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12939,7 +13449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12954,7 +13464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12969,7 +13479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12984,7 +13494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12999,7 +13509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13014,7 +13524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13029,7 +13539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.7867</x:v>
+        <x:v>     14.5862</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13044,7 +13554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.7867</x:v>
+        <x:v>     14.5862</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13059,7 +13569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13074,7 +13584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13089,7 +13599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13104,7 +13614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13119,7 +13629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.5238</x:v>
+        <x:v>     18.4131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13134,7 +13644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.5238</x:v>
+        <x:v>     18.4131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13149,7 +13659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     21.5238</x:v>
+        <x:v>     18.4131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13164,7 +13674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13179,7 +13689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13194,7 +13704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13209,7 +13719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13224,7 +13734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13239,7 +13749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13254,7 +13764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13269,7 +13779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13284,7 +13794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13299,7 +13809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.7721</x:v>
+        <x:v>     31.5798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13314,7 +13824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.4377</x:v>
+        <x:v>     32.5040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13329,7 +13839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13344,7 +13854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13359,7 +13869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13374,7 +13884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13389,7 +13899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13404,7 +13914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13419,7 +13929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13434,7 +13944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13449,7 +13959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13464,7 +13974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13479,7 +13989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13494,7 +14004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13509,7 +14019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13524,7 +14034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13539,7 +14049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.1178</x:v>
+        <x:v>     21.7346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13554,7 +14064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.3660</x:v>
+        <x:v>     22.3284</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13569,7 +14079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.3660</x:v>
+        <x:v>     22.3284</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13584,7 +14094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13599,7 +14109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13614,7 +14124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13629,7 +14139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -13644,7 +14154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_65049_completo.xlsx
+++ b/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_65049_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Refc22cab762c4334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4a55f4f08f534b3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2901 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
